--- a/internal_doc/05.测试设计/story/alter/alter测试用例（异常测试）.xlsx
+++ b/internal_doc/05.测试设计/story/alter/alter测试用例（异常测试）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>name</t>
   </si>
@@ -151,6 +151,26 @@
   <si>
     <t>1、节点故障时，更新操作失败，返回对应错误信息。查看修改属性值已更新（失败不回滚）
 2、故障恢复后，再次执行更新操作成功，查看domain对应属性值已为更新值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改cl压缩类型属性，数据组所有节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、修改集合中compressionType值，分别验证如下场景：
+a、snappy修改为lzw
+b、lzw修改为snappy
+2、插入新数据
+3、数据组所有节点异常重启
+4、故障恢复后，检查数据压缩结果
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、故障恢复后，查看压缩类型为更新值（快照8和快照4查看压缩属性信息）
+2、直连数据组主备数据节点dump日志查看记录压缩类型正确（修改前压缩类型为原值，修改后压缩类型为更新值）
+3、查询数据信息正确，和插入数据信息一致；查看主备节点间数据一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -365,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I6" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I7" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -685,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -753,9 +773,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="94.5">
+    <row r="3" spans="1:9" ht="108">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -770,18 +790,18 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="81">
+    <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -796,18 +816,18 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="94.5">
+    <row r="5" spans="1:9" ht="81">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -822,10 +842,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -833,27 +853,53 @@
     </row>
     <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="94.5">
+      <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I7" s="3">
         <v>1</v>
       </c>
     </row>
